--- a/docs/CodeSystem-space-motion-sickness-cs.xlsx
+++ b/docs/CodeSystem-space-motion-sickness-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-space-motion-sickness-cs.xlsx
+++ b/docs/CodeSystem-space-motion-sickness-cs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="54">
   <si>
     <t>Property</t>
   </si>
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/CodeSystem/space-motion-sickness-cs</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/CodeSystem/space-motion-sickness-cs</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,13 +54,13 @@
     <t>Experimental</t>
   </si>
   <si>
-    <t>false</t>
+    <t>true</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,10 +93,10 @@
     <t>Copyright</t>
   </si>
   <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
+  </si>
+  <si>
     <t>Case Sensitive</t>
-  </si>
-  <si>
-    <t>true</t>
   </si>
   <si>
     <t>Value Set (all codes)</t>
@@ -421,14 +421,16 @@
       <c r="A14" t="s" s="2">
         <v>25</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>26</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
